--- a/.claude/build/research/KPC_Research_Worklist_Round9H_History.xlsx
+++ b/.claude/build/research/KPC_Research_Worklist_Round9H_History.xlsx
@@ -523,7 +523,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>1. Official sources only: the park's own page (parks.ky.gov, nps.gov, fs.usda.gov, eec.ky.gov nature preserves, the agency that runs it) or a .gov / official state history page (for example the Kentucky Historical Society or a state historical marker page). No Wikipedia, travel sites, blogs, AI summaries.</t>
+          <t>1. Official sources only: the park's own page (parks.ky.gov, nps.gov, fs.usda.gov, eec.ky.gov nature preserves, the agency that runs it) or the Kentucky Historical Society, a state agency: history.ky.gov, its historical markers (history.ky.gov/markers) and ExploreKYHistory (explorekyhistory.ky.gov). A historical marker near or about the park is a good source: link the marker's own page. No Wikipedia, travel sites, blogs, AI summaries.</t>
         </is>
       </c>
     </row>
